--- a/internal_doc/05.测试设计/参数校验/测试用例/元数据（CS）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/元数据（CS）参数校验测试用例.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="71">
   <si>
     <t>name</t>
   </si>
@@ -74,203 +74,151 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>重要性（1高2中3低）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试用例摘要（测试目的）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCS，覆盖name/options有效字符和边界</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCS，name重复</t>
+  </si>
+  <si>
+    <t>createCS，name字符无效</t>
+  </si>
+  <si>
+    <t>createCS，name长度无效</t>
+  </si>
+  <si>
+    <t>createCS，格式错误</t>
+  </si>
+  <si>
+    <t>语法：db.createCS(&lt; name &gt;,[ options ])
+参数规格：
+name：string，必填，全局唯一，不能是空串，含点（.）或者美元符号（$）。且长度不超过127B。
+options:PageSize：默认为65536B，只能选填0，4096，8192，16384，32768，65536之一，0即默认为65536。非必填
+为兼容较早版本接口，db.createCS(&lt; name &gt;,[ PageSize ]) 同样可以工作。
+options:Domain，所属CS必须已经存在，且不能为 SYSDOMAIN。非必填
+options:LobPageSize，只能选填0，4096，8192，16384，32768，65536，131072，262144，524288之一，0即为默认值262144。非必填</t>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CS，输入有效的name、groups、Autosplit创建CS，如：
+db.createCS("testCS")
+2、重复步骤1，创建name相同的CS
+3、检查执行结果</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1、首次创建name唯一的CS，创建成功
+2、重复创建相同name的CS，创建失败，返回结果报错，并提示CS名已存在，提示信息合理准确
+</t>
+  </si>
+  <si>
+    <t>1、CS创建失败，提示参数不合法，提示信息合理准确
+2、日志打印信息合理准确</t>
+  </si>
+  <si>
+    <t>1、CS创建失败，提示参数超出长度，提示信息合理准确
+2、日志打印信息合理准确</t>
+  </si>
+  <si>
+    <t>1、CS创建失败，提示参数错误，提示信息合理准确
+2、日志打印信息合理准确</t>
+  </si>
+  <si>
+    <t>1、CS创建失败，提示系统CS不能删除，提示信息合理准确
+2、日志打印信息合理准确</t>
+  </si>
+  <si>
+    <t>1、CS获取失败，提示参数错误，提示信息合理准确
+2、日志打印信息合理准确</t>
+  </si>
+  <si>
+    <t>1、CS获取成功，指定的CS被直接忽略，返回结果显示所有CS（非系统CS）</t>
+  </si>
+  <si>
     <t>1、sdb运行正常
-2、sdb已存在数据组group1、group2、group3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重要性（1高2中3低）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1、域创建成功，执行db.getDomain(&lt; name &gt;)条件查询可以查看到新创建的域。
-2、创建CS，指定域为新创建的域，CS创建成功。
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createDomain，覆盖name/groups/options有效字符和边界</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createDomain，name重复</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建域，输入有效的name、groups、Autosplit创建域，如：
-db.createDomain('dm',['rg1','rg2'],{AutoSplit:true})
-2、重复步骤1，创建name相同的域
-3、检查执行结果</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1、首次创建name唯一的域，创建成功
-2、重复创建相同name的域，创建失败，返回结果报错，并提示域名已存在，提示信息合理准确
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createDomain，name字符无效</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、域创建失败，提示参数不合法，提示信息合理准确
-2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createDomain，name长度无效</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createDomain，name参数不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建域，输入name长度无效，覆盖如下无效取值：
+2、sdb已存在数据组group1、group2、group3
+3、sdb已存在域domain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CS，输入name、PageSize、Domain、LobPageSize有效参数创建CS，规格如下：
+name覆盖如下取值：
+  a.1字节的有效字符，如：a 或 *
+  b.127字节的有效字符，覆盖所有支持的有效字符，如：“123-test-中文。~!@#%^&amp;*()_+-=\][{}|,/&lt;&gt;?~·！@#￥%……&amp;*（）——+《》{}|【】、，。、~_127B”
+PageSize覆盖如下取值：0、4096、8192、16384、32768、65536
+Domain覆盖如下取值:已存在的CS，非系统CS
+LobPageSize覆盖如下取值：0、4096、8192、16384、32768、65536、131072、262144、524288
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CS，输入name字符无效，覆盖如下无效取值：
+  a.包含（.）
+  b.包含$
+如：
+db.createCS('test.cs')
+db.createCS('test$cs')
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CS，输入name长度无效，覆盖如下无效取值：
   a.空串
   b.128字节
 如：
-db.createDomain('',['rg1'])
+db.createCS('')  或  db.createCS()   或  为128字节的有效字符
 3、检查执行结果</t>
-  </si>
-  <si>
-    <t>1、域创建失败，提示参数超出长度，提示信息合理准确
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CS，不输入name，如：
+db.createCS({PageSize:4096,Domain:"domain"})
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCS，name参数不存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCS，options:PageSize无效取值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CS创建成功，执行db.listCollectionSpaces或db.snapshot可以查看到新创建的CS。
+检查PageSize、LobPageSize默认取值。
+2、在CS下创建CL，CL创建成功。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCS，options:Domain指定的域不存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，options:Domain指定的域不存在，如：
+db.createCS('testCS',{Domain:dm})，其中dm在sdb不存在
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CS创建失败，提示域不存在，提示信息合理准确
 2、日志打印信息合理准确</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>createDomain，groups指定的组不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建域，输入name字符无效，覆盖如下无效取值：
-  a.包含（.）
-  b.包含$
-如：
-db.createDomain('d.m',['rg1'])
-db.createDomain('d$m',['rg1'])
-2、检查执行结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，创建域，不输入name，如：
-db.createDomain(['rg1'],{AutoSplit:true})
-2、检查执行结果</t>
-  </si>
-  <si>
-    <t>1、域创建失败，提示参数错误，提示信息合理准确
-2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建域，指定的组不存在，如：
-db.createDomain('dm',['rg1','gr2'])，其中rg2在CM中不存在
-2、检查执行结果</t>
-  </si>
-  <si>
-    <t>1、域创建失败，提示rg2组不存在，提示信息合理准确
-2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createDomain，groups取值为空串</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建域，groups取值为空串，如：
-db.createDomain('dm',[''])
-2、检查执行结果</t>
-  </si>
-  <si>
-    <t>createDomain，groups参数不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建域，groups参数不存在，如：
-db.createDomain('dm',{AutoSplit:true})
-2、检查执行结果</t>
-  </si>
-  <si>
-    <t>createDomain，options:AutoSplit取值非法</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建域，输入name、groups、AutoSplit有效参数创建域，规格如下：
-name覆盖如下取值：
-  a.1字节的有效字符，如：a 或 *
-  b.127字节的有效字符，覆盖所有支持的有效字符，如：“123-test-中文。~!@#$%^&amp;*()_+-=\][{}|,./&lt;&gt;?~·！@#￥%……&amp;*（）——+《》{}|【】、，。、~._.....127B”
-groups覆盖如下数值个数：1、10（没限制，随机取值）
-Autosplit覆盖如下取值:
-   a.AutoSplit:true|false
-   b.不指定AutoSplit
-   c.AutoSplit：yes|no、T|F、0|-1、Y|N
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建域，AutoSplit取值非法，覆盖如下取值：
-  a.非bool型取值，如test_123
-  b.空串
-如：
-db.createDomain('dm',['rg1']),{AutoSplit:test_123})
-db.createDomain('dm',['rg1']),{AutoSplit:)
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createDomain，格式错误</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建域，参数格式错误，覆盖如下参数格式：
-  a.引号使用错误，如字符串类型不带引号输入、bool类型带引号输入
-  b.多参数
-如：
-db.createDomain(dm,[rg1],{AutoSplit:"true"})
-db.createDomain('dm',['rg1']),{AutoSplit:true,true)
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试用例摘要（测试目的）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dropDomain，删除不存在的域</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，删除不存在的域，如：
-db.dropDomain("test"),其中test域在sdb不存在
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、域创建失败，提示域不存在，提示信息合理准确
-2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dropDomain，删除非空的域</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，删除非空的域，如：
-db.dropDomain("test"),其中test中存在CS
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、域创建失败，提示域非空，提示信息合理准确
-2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dropDomain，删除系统域</t>
+    <t>createCS，options:Domain指定的域为系统域</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>1、进入sdb，删除</t>
+      <t>1、进入sdb，options:Domain指定的域为系统域，如：
+db.createCS('testCS',{Domain:dm})，其中dm为</t>
     </r>
     <r>
       <rPr>
@@ -292,257 +240,180 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>，如：
-db.dropDomain("test"),其中test为系统域
+      <t xml:space="preserve">
 2、检查执行结果</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、域创建失败，提示系统域不能删除，提示信息合理准确
-2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>语法：db.createDomain(&lt; name &gt;,&lt; groups &gt;,[ options ])
-参数规格：
-name：string，必填，全局唯一，参数规则资料没给说明，参考createCS：不能是空串，含点（.）或者美元符号（$）。且长度不超过127B。
-group：Json数组，必填，必须是已存在的组
-AutoSplit:true|false，默认为false，非必填</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>语法：db.dropDomain(&lt; name &gt;)
-参数规格：
-name：string，必填，不能删除不为空的域；不能删除系统域；域必须存在。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>语法：db.getDomain(&lt; name &gt;)
-参数规格：
-name：string，必填，获取已存在的域。不能获取系统域。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，获取指定域，不指定域名，如：
-db.dropDomain()
+    <t>createCS，options:Domain取值为空串</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，options:Domain取值为空串，如：
+db.createCS('testCS',{Domain:})
+db.createCS('testCS',{Domain:''})
 2、检查执行结果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>getDomain，获取不存在的域</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dropDomain，指定域名为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，删除域，域名为空，覆盖如下取值：
-db.dropDomain("")
-db.dropDomain()
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>getDomain，指定的域名为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、域获取失败，提示域不存在，提示信息合理准确
-2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、域获取失败，提示参数错误，提示信息合理准确
-2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>listDomains，加条件查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>语法：db.listDomains()
-无参数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，获取指定的域，域名为空，覆盖如下取值：
-db.getDomain("")
-db.getDomain()
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、域获取成功，指定的域被直接忽略，返回结果显示所有域（非系统域）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，获取所有域（非系统域），指定域名，覆盖如下取值：
-  a.指定已存在的域名
+    <t>createCS，options:LobPageSize无效取值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CS，输入LobPageSize无效取值，覆盖如下取值：
+  a.无效取值：4096.5、-4096、4096.
   b.空串
 如：
-db.listDomains("dm")
-db.listDomains("")
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>语法：domain.alter(&lt; options &gt;)，必须指定一个参数
-参数规格：
-options:Groups，删除复制组前必须保证其不包含任何数据。
-options:Autosplit，bool类型，true|false，非必填</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、域修改失败，提示rg4不存在，提示信息合理准确
-2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、域修改失败，提示参数错误，提示信息合理准确
-2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>domain.alter，指定Groups和AutoSplit参数正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>domain.alter，Groups指定不存在的组</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>domain.alter，Groups为空串</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建域，如：
-var domain = db.createDomain('domain',['rg1','rg2']，AutoSplit:true)
-2、修改域，Groups和AutoSplit修改正确，覆盖如下取值：
-  a.Groups指定所有组，AutoSplit:true
-  b.AutoSplit:false
-如：
-domain.alter({Groups:['rg1','rg2','rg3']},{AutoSplit:true})
-domain.alter({AutoSplit:false})
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、域修改成功，db.listDomains()查看域修改正确
-2、做如下操作，检查域修改后是否正确可用，如：
-  创建CS，并指定域为domain
-  创建CL，不指定AutoSplit，指定为hash切分
-  插入批量数据
-若修改后域为自动切分，则数据按均匀落在不同的组，域修改正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建域，如：
-var domain = db.createDomain('domain',['rg1'])
-2、修改dm域，Groups指定不存在的组，如：
-domain.alter({Groups:['rg2','rg4']})，其中rg4为不存在的组
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建域，如：
-var domain = db.createDomain('domain',['rg1'])
-2、修改域，Groups指定为空串，如：
-domain.alter({Groups:['']})
-domain.alter({Groups:})
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>domain.alter，AutoSplit取值非bool型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>domain.alter，AutoSplit为空串</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建域，如：
-var domain = db.createDomain('domain',['rg1'])
-2、修改域，AutoSplit取值非法，如：
-domain.alter({AutoSplit:test})
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建域，如：
-var domain = db.createDomain('domain',['rg1'])
-2、修改域，AutoSplit为空串，如：
-domain.alter({AutoSplit:})
-domain.alter({AutoSplit:''})
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>domain.alter，不指定任何参数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建域，如：
-var domain = db.createDomain('domain',['rg1'])
-2、修改域，不指定任何参数，如：
-domain.alter()
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>domain.listCollections，加条件查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>语法：domain.listCollections()
-无参数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>语法：domain.listCollectionSpaces()
-无参数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>domain.listCollectionSpaces，加条件查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、集合获取成功，指定的CS被直接忽略，返回结果显示该域中的所有CS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、集合获取成功，指定的CL被直接忽略，返回结果显示该域中的所有CL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建域，如：
-var domain = db.createDomain('domain',['rg1'])
-2、创建CS，指定域为domain
-3、在CS创建CL
-4、domain.listCollections获取域中所有集合，指定集合名词，覆盖如下取值：
-  a.指定已存在的集合
+db.createCS('testCS',{LobPageSize:4096.5})  
+db.createCS('testCS',{LobPageSize:})
+db.createCS('testCS',{LobPageSize:''})
+3、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CS，输入PageSize无效取值，覆盖如下取值：
+  a.无效取值：4096.5、-4096、4096.
   b.空串
 如：
-domain.listCollections("testCL")
-domain.listCollections("")
-5、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建域，如：
-var domain = db.createDomain('domain',['rg1'])
-2、创建CS，指定域为domain
-3、domain.listCollections获取域中所有集合空间，指定集合空间名词，覆盖如下取值：
-  a.指定已存在的集合空间
+db.createCS('testCS',{PageSize:4096.5})  
+db.createCS('testCS',{PageSize:})
+3、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CS，参数格式错误，覆盖如下参数格式：
+  a.引号使用错误，如字符串类型不带引号输入、bool类型带引号输入
+  b.多参数
+  c.为空
+如：
+db.createCS("testCS",{PageSize:"4096",Domain:domain,LobPageSize:"4096"})
+db.createCS("testCS",{PageSize:4096,Domain:"domain",LobPageSize:4096,PageSize:2048})
+db.createCS('testCS',{})
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dropCS，删除系统CS</t>
+  </si>
+  <si>
+    <t>dropCS，指定CS名为空</t>
+  </si>
+  <si>
+    <t>1、进入sdb，删除CS，CS名为空，覆盖如下取值：
+db.dropCS("")
+db.dropCS()
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>语法：db.dropCS(&lt; name &gt;)
+参数规格：
+name：string，必填，CS必须存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，删除不存在的CS，如：
+db.dropCS("testCS"),其中testCS在sdb不存在
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>dropCS，删除不存在的CS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dropCS，删除为空和不为空的CS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，删除为空和不为空的CS，如：
+db.dropCS("testCS_01"),其中testCS_01中存在CL
+db.dropCS("testCS_02"),其中testCS_02中不存在CL
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CS创建失败，提示CS不存在，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1、CS删除成功，db.list(4)或db.list(5)查看CS以及CS下CL已全部删除
+2、查看</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CS相关配置文件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>已删除干净</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，删除系统CS，如：
+db.dropCS("testCS"),其中testCS为系统CS
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getCS，获取不存在的CS</t>
+  </si>
+  <si>
+    <t>语法：db.getCS(&lt; name &gt;)
+参数规格：
+name：string，必填，获取已存在的CS。不能获取系统CS。</t>
+  </si>
+  <si>
+    <t>getCS，指定的CS名为空</t>
+  </si>
+  <si>
+    <t>1、进入sdb，获取指定的CS，CS名为空，覆盖如下取值：
+db.getCS("")
+db.getCS()
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、CS获取失败，提示CS不存在，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，获取指定CS，不指定CS名，如：
+db.dropCS("testCS")，其中testCS在sdb不存在
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>listCollectionSpaces，加条件查询</t>
+  </si>
+  <si>
+    <t>语法：db.listCollectionSpaces()
+无参数</t>
+  </si>
+  <si>
+    <t>1、进入sdb，获取所有CS（非系统CS），指定CS名，覆盖如下取值：
+  a.指定已存在的CS名
   b.空串
 如：
-domain.listCollectionSpaces("testCS")
-domain.listCollectionSpaces("")
-4、检查执行结果</t>
+db.listCollectionSpaces("testCS")，其中testCS在sdb存在
+db.listCollectionSpaces("")
+2、检查执行结果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -601,7 +472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -623,6 +494,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -713,8 +587,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I27" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I20" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I20"/>
   <tableColumns count="9">
     <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
@@ -1033,7 +907,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="26.375" style="1" customWidth="1"/>
@@ -1080,7 +954,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>9</v>
@@ -1089,7 +963,7 @@
         <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>13</v>
@@ -1104,15 +978,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="256.5">
+    <row r="3" spans="1:9" ht="182.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D3" s="4">
         <v>1</v>
@@ -1123,22 +997,22 @@
       <c r="F3" s="4">
         <v>1</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>40</v>
+      <c r="G3" s="8" t="s">
+        <v>33</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="I3" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="81">
+    <row r="4" spans="1:9" ht="67.5">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D4" s="4">
         <v>1</v>
@@ -1146,19 +1020,19 @@
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I4" s="4"/>
     </row>
     <row r="5" spans="1:9" ht="108">
       <c r="A5" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
@@ -1166,20 +1040,20 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I5" s="4"/>
     </row>
-    <row r="6" spans="1:9" ht="94.5">
+    <row r="6" spans="1:9" ht="108">
       <c r="A6" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D6" s="4">
         <v>1</v>
@@ -1187,19 +1061,19 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="I6" s="4"/>
     </row>
-    <row r="7" spans="1:9" ht="54">
+    <row r="7" spans="1:9" ht="67.5">
       <c r="A7" s="2" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D7" s="4">
         <v>1</v>
@@ -1207,19 +1081,19 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I7" s="4"/>
     </row>
-    <row r="8" spans="1:9" ht="54">
+    <row r="8" spans="1:9" ht="108">
       <c r="A8" s="2" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
@@ -1227,19 +1101,19 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="2" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:9" ht="54">
+    <row r="9" spans="1:9" ht="67.5">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
@@ -1247,19 +1121,19 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="I9" s="4"/>
     </row>
-    <row r="10" spans="1:9" ht="54">
+    <row r="10" spans="1:9" ht="67.5">
       <c r="A10" s="2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -1267,19 +1141,19 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I10" s="4"/>
     </row>
-    <row r="11" spans="1:9" ht="135">
+    <row r="11" spans="1:9" ht="67.5">
       <c r="A11" s="2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D11" s="4">
         <v>1</v>
@@ -1287,19 +1161,19 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I11" s="4"/>
     </row>
-    <row r="12" spans="1:9" ht="148.5">
+    <row r="12" spans="1:9" ht="135">
       <c r="A12" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -1307,22 +1181,19 @@
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:9" ht="81">
+    <row r="13" spans="1:9" ht="189">
       <c r="A13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
@@ -1330,19 +1201,19 @@
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:9" ht="54">
+    <row r="14" spans="1:9" ht="81">
       <c r="A14" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
@@ -1350,260 +1221,138 @@
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:9" ht="54">
+    <row r="15" spans="1:9" ht="67.5">
       <c r="A15" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D15" s="4">
         <v>1</v>
       </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
       <c r="G15" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>53</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:9" ht="67.5">
       <c r="A16" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D16" s="4">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="67.5">
       <c r="A17" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="67.5">
       <c r="A18" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D18" s="4">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="108">
+    </row>
+    <row r="19" spans="1:8" ht="67.5">
       <c r="A19" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" s="4">
-        <v>1</v>
-      </c>
-      <c r="G19" s="2" t="s">
+      <c r="H19" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="121.5">
+      <c r="A20" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="175.5">
-      <c r="A20" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>69</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D20" s="4">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="94.5">
-      <c r="A21" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D21" s="4">
-        <v>1</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H21" s="1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="94.5">
-      <c r="A22" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="4">
-        <v>1</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="81">
-      <c r="A23" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="4">
-        <v>1</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="94.5">
-      <c r="A24" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="81">
-      <c r="A25" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D25" s="4">
-        <v>1</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="162">
-      <c r="A26" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26" s="4">
-        <v>1</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="175.5">
-      <c r="A27" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="2"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="2"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="2"/>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="2"/>
+      <c r="H20" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="2"/>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="2"/>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="2"/>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/05.测试设计/参数校验/测试用例/元数据（CS）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/元数据（CS）参数校验测试用例.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="84">
   <si>
     <t>name</t>
   </si>
@@ -82,10 +82,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>createCS，覆盖name/options有效字符和边界</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>createCS，name重复</t>
   </si>
   <si>
@@ -96,15 +92,6 @@
   </si>
   <si>
     <t>createCS，格式错误</t>
-  </si>
-  <si>
-    <t>语法：db.createCS(&lt; name &gt;,[ options ])
-参数规格：
-name：string，必填，全局唯一，不能是空串，含点（.）或者美元符号（$）。且长度不超过127B。
-options:PageSize：默认为65536B，只能选填0，4096，8192，16384，32768，65536之一，0即默认为65536。非必填
-为兼容较早版本接口，db.createCS(&lt; name &gt;,[ PageSize ]) 同样可以工作。
-options:Domain，所属CS必须已经存在，且不能为 SYSDOMAIN。非必填
-options:LobPageSize，只能选填0，4096，8192，16384，32768，65536，131072，262144，524288之一，0即为默认值262144。非必填</t>
   </si>
   <si>
     <t>1、进入sdb，创建CS，输入有效的name、groups、Autosplit创建CS，如：
@@ -144,17 +131,6 @@
     <t>1、sdb运行正常
 2、sdb已存在数据组group1、group2、group3
 3、sdb已存在域domain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CS，输入name、PageSize、Domain、LobPageSize有效参数创建CS，规格如下：
-name覆盖如下取值：
-  a.1字节的有效字符，如：a 或 *
-  b.127字节的有效字符，覆盖所有支持的有效字符，如：“123-test-中文。~!@#%^&amp;*()_+-=\][{}|,/&lt;&gt;?~·！@#￥%……&amp;*（）——+《》{}|【】、，。、~_127B”
-PageSize覆盖如下取值：0、4096、8192、16384、32768、65536
-Domain覆盖如下取值:已存在的CS，非系统CS
-LobPageSize覆盖如下取值：0、4096、8192、16384、32768、65536、131072、262144、524288
-2、检查执行结果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -414,6 +390,95 @@
 db.listCollectionSpaces("testCS")，其中testCS在sdb存在
 db.listCollectionSpaces("")
 2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCS，覆盖name有效字符和边界</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>options:PageSize：默认为65536B，只能选填0，4096，8192，16384，32768，65536之一，0即默认为65536。非必填
+为兼容较早版本接口，db.createCS(&lt; name &gt;,[ PageSize ]) 同样可以工作。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdb运行正常
+2、sdb已存在数据组group1、group2、group3
+3、sdb已存在域domain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCS，覆盖options：PageSize有效字符和边界</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>options:Domain，所属CS必须已经存在，且不能为 SYSDOMAIN。非必填</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>options:LobPageSize，只能选填0，4096，8192，16384，32768，65536，131072，262144，524288之一，0即为默认值262144。非必填</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCS，覆盖options:Domain有效字符和边界</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCS，覆盖options:LobPageSize有效字符和边界</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：db.createCS(&lt; name &gt;,[ options ])
+参数规格：
+name：string，必填，全局唯一，不能是空串，含点（.）或者美元符号（$）。且长度不超过127B。
+option非必填</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CS，输入name有效字符和长度参数创建CS，规格如下：
+name覆盖如下取值：
+  a.1字节的有效字符，如：a 或 *
+  b.127字节的有效字符，覆盖所有支持的有效字符，如：“123-test-中文。~!@#%^&amp;*()_+-=\][{}|,/&lt;&gt;?~·！@#￥%……&amp;*（）——+《》{}|【】、，。、~_127B”
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CS，输入name、PageSize有效参数创建CS，规格如下：
+  name取任意有效值；
+  PageSize覆盖如下取值：0、4096、8192、16384、32768、65536
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CS创建成功，执行db.listCollectionSpaces或db.snapshot可以查看到新创建的CS。
+检查PageSize值与创建CS设置的值一致。
+2、在CS下创建CL，CL创建成功。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CS，输入name、Domain有效参数创建CS，规格如下：
+  name取任意有效值；
+  Domain覆盖如下取值:已存在的CS，非系统CS
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CS创建成功，执行db.listCollectionSpaces或db.snapshot可以查看到新创建的CS。
+检查Domain与创建CS设置的Domain一致。
+2、在CS下创建CL，CL创建成功。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CS，输入name、PageSize、Domain、LobPageSize有效参数创建CS，规格如下：
+  name取任意有效值；
+  LobPageSize覆盖如下取值：0、4096、8192、16384、32768、65536、131072、262144、524288
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CS创建成功，执行db.listCollectionSpaces或db.snapshot可以查看到新创建的CS。
+检查LobPageSize与创建CS设置的LobPageSize值一致。
+2、在CS下创建CL，CL创建成功。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -472,7 +537,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -494,9 +559,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -587,8 +649,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I20" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I23" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I23"/>
   <tableColumns count="9">
     <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
@@ -907,7 +969,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="26.375" style="1" customWidth="1"/>
@@ -978,15 +1040,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="182.25" customHeight="1">
+    <row r="3" spans="1:9" ht="121.5">
       <c r="A3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>23</v>
+        <v>68</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>76</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="D3" s="4">
         <v>1</v>
@@ -997,83 +1059,85 @@
       <c r="F3" s="4">
         <v>1</v>
       </c>
-      <c r="G3" s="8" t="s">
-        <v>33</v>
+      <c r="G3" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I3" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="67.5">
+    <row r="4" spans="1:9" ht="94.5">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>71</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="2" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" spans="1:9" ht="108">
+    <row r="5" spans="1:9" ht="81">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>74</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="2" t="s">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="I5" s="4"/>
     </row>
     <row r="6" spans="1:9" ht="108">
       <c r="A6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="7"/>
+        <v>75</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>73</v>
+      </c>
       <c r="C6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="2" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="I6" s="4"/>
     </row>
     <row r="7" spans="1:9" ht="67.5">
       <c r="A7" s="2" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D7" s="4">
         <v>1</v>
@@ -1081,19 +1145,19 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="2" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" ht="108">
       <c r="A8" s="2" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
@@ -1101,19 +1165,20 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="2" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:9" ht="67.5">
+    <row r="9" spans="1:9" ht="108">
       <c r="A9" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B9" s="7"/>
       <c r="C9" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
@@ -1121,19 +1186,19 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:9" ht="67.5">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -1141,19 +1206,19 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I10" s="4"/>
     </row>
-    <row r="11" spans="1:9" ht="67.5">
+    <row r="11" spans="1:9" ht="108">
       <c r="A11" s="2" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D11" s="4">
         <v>1</v>
@@ -1164,16 +1229,16 @@
         <v>46</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I11" s="4"/>
     </row>
-    <row r="12" spans="1:9" ht="135">
+    <row r="12" spans="1:9" ht="67.5">
       <c r="A12" s="2" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -1181,19 +1246,19 @@
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="2" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:9" ht="189">
+    <row r="13" spans="1:9" ht="67.5">
       <c r="A13" s="2" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
@@ -1201,19 +1266,19 @@
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="2" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:9" ht="81">
+    <row r="14" spans="1:9" ht="67.5">
       <c r="A14" s="2" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
@@ -1221,22 +1286,19 @@
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:9" ht="67.5">
+    <row r="15" spans="1:9" ht="135">
       <c r="A15" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D15" s="4">
         <v>1</v>
@@ -1244,115 +1306,178 @@
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I15" s="4"/>
+    </row>
+    <row r="16" spans="1:9" ht="189">
+      <c r="A16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="4"/>
+    </row>
+    <row r="17" spans="1:9" ht="81">
+      <c r="A17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I17" s="4"/>
+    </row>
+    <row r="18" spans="1:9" ht="67.5">
+      <c r="A18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I18" s="4"/>
+    </row>
+    <row r="19" spans="1:9" ht="67.5">
+      <c r="A19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="67.5">
+      <c r="A20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="67.5">
+      <c r="A21" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="I15" s="4"/>
-    </row>
-    <row r="16" spans="1:9" ht="67.5">
-      <c r="A16" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="4">
-        <v>1</v>
-      </c>
-      <c r="G16" s="2" t="s">
+      <c r="B21" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="4">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="67.5">
+      <c r="A22" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="C22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="4">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="121.5">
+      <c r="A23" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="4">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="67.5">
-      <c r="A17" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="4">
-        <v>1</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="67.5">
-      <c r="A18" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" s="4">
-        <v>1</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="67.5">
-      <c r="A19" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="4">
-        <v>1</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="121.5">
-      <c r="A20" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" s="4">
-        <v>1</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="2"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="2"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="2"/>
-    </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:9">
       <c r="A24" s="2"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="2"/>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="2"/>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/05.测试设计/参数校验/测试用例/元数据（CS）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/元数据（CS）参数校验测试用例.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="85">
   <si>
     <t>name</t>
   </si>
@@ -114,10 +114,6 @@
   </si>
   <si>
     <t>1、CS创建失败，提示参数错误，提示信息合理准确
-2、日志打印信息合理准确</t>
-  </si>
-  <si>
-    <t>1、CS创建失败，提示系统CS不能删除，提示信息合理准确
 2、日志打印信息合理准确</t>
   </si>
   <si>
@@ -305,11 +301,6 @@
 db.dropCS("testCS_01"),其中testCS_01中存在CL
 db.dropCS("testCS_02"),其中testCS_02中不存在CL
 2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、CS创建失败，提示CS不存在，提示信息合理准确
-2、日志打印信息合理准确</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -479,6 +470,21 @@
     <t>1、CS创建成功，执行db.listCollectionSpaces或db.snapshot可以查看到新创建的CS。
 检查LobPageSize与创建CS设置的LobPageSize值一致。
 2、在CS下创建CL，CL创建成功。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CS删除失败，提示CS不存在，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CS删除失败，提示系统CS不能删除，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CS删除失败，提示参数错误，提示信息合理准确
+2、日志打印信息合理准确</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1042,13 +1048,13 @@
     </row>
     <row r="3" spans="1:9" ht="121.5">
       <c r="A3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="D3" s="4">
         <v>1</v>
@@ -1060,10 +1066,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I3" s="4">
         <v>1</v>
@@ -1071,64 +1077,64 @@
     </row>
     <row r="4" spans="1:9" ht="94.5">
       <c r="A4" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I4" s="4"/>
     </row>
     <row r="5" spans="1:9" ht="81">
       <c r="A5" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I5" s="4"/>
     </row>
     <row r="6" spans="1:9" ht="108">
       <c r="A6" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I6" s="4"/>
     </row>
@@ -1137,7 +1143,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" s="4">
         <v>1</v>
@@ -1157,7 +1163,7 @@
         <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
@@ -1165,7 +1171,7 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>24</v>
@@ -1178,7 +1184,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
@@ -1186,7 +1192,7 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>25</v>
@@ -1195,10 +1201,10 @@
     </row>
     <row r="10" spans="1:9" ht="67.5">
       <c r="A10" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -1206,7 +1212,7 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>26</v>
@@ -1215,10 +1221,10 @@
     </row>
     <row r="11" spans="1:9" ht="108">
       <c r="A11" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D11" s="4">
         <v>1</v>
@@ -1226,7 +1232,7 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>26</v>
@@ -1235,10 +1241,10 @@
     </row>
     <row r="12" spans="1:9" ht="67.5">
       <c r="A12" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -1246,19 +1252,19 @@
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:9" ht="67.5">
       <c r="A13" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
@@ -1266,7 +1272,7 @@
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>26</v>
@@ -1275,10 +1281,10 @@
     </row>
     <row r="14" spans="1:9" ht="67.5">
       <c r="A14" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
@@ -1286,7 +1292,7 @@
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>26</v>
@@ -1295,10 +1301,10 @@
     </row>
     <row r="15" spans="1:9" ht="135">
       <c r="A15" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D15" s="4">
         <v>1</v>
@@ -1306,7 +1312,7 @@
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>26</v>
@@ -1318,7 +1324,7 @@
         <v>21</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" s="4">
         <v>1</v>
@@ -1326,7 +1332,7 @@
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>26</v>
@@ -1335,10 +1341,10 @@
     </row>
     <row r="17" spans="1:9" ht="81">
       <c r="A17" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
@@ -1346,22 +1352,22 @@
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="I17" s="4"/>
     </row>
     <row r="18" spans="1:9" ht="67.5">
       <c r="A18" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" s="4">
         <v>1</v>
@@ -1369,102 +1375,102 @@
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" ht="67.5">
       <c r="A19" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19" s="4">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="67.5">
       <c r="A20" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" s="4">
-        <v>1</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="H20" s="2" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="67.5">
       <c r="A21" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D21" s="4">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="67.5">
       <c r="A22" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D22" s="4">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="121.5">
       <c r="A23" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="4">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="4">
-        <v>1</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="H23" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:9">

--- a/internal_doc/05.测试设计/参数校验/测试用例/元数据（CS）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/元数据（CS）参数校验测试用例.xlsx
@@ -82,18 +82,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>createCS，name重复</t>
-  </si>
-  <si>
-    <t>createCS，name字符无效</t>
-  </si>
-  <si>
-    <t>createCS，name长度无效</t>
-  </si>
-  <si>
-    <t>createCS，格式错误</t>
-  </si>
-  <si>
     <t>1、进入sdb，创建CS，输入有效的name、groups、Autosplit创建CS，如：
 db.createCS("testCS")
 2、重复步骤1，创建name相同的CS
@@ -155,24 +143,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>createCS，name参数不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCS，options:PageSize无效取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、CS创建成功，执行db.listCollectionSpaces或db.snapshot可以查看到新创建的CS。
 检查PageSize、LobPageSize默认取值。
 2、在CS下创建CL，CL创建成功。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>createCS，options:Domain指定的域不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，options:Domain指定的域不存在，如：
 db.createCS('testCS',{Domain:dm})，其中dm在sdb不存在
 2、检查执行结果</t>
@@ -181,10 +157,6 @@
   <si>
     <t>1、CS创建失败，提示域不存在，提示信息合理准确
 2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCS，options:Domain指定的域为系统域</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -218,18 +190,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>createCS，options:Domain取值为空串</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，options:Domain取值为空串，如：
 db.createCS('testCS',{Domain:})
 db.createCS('testCS',{Domain:''})
 2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCS，options:LobPageSize无效取值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -240,16 +204,6 @@
 db.createCS('testCS',{LobPageSize:4096.5})  
 db.createCS('testCS',{LobPageSize:})
 db.createCS('testCS',{LobPageSize:''})
-3、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CS，输入PageSize无效取值，覆盖如下取值：
-  a.无效取值：4096.5、-4096、4096.
-  b.空串
-如：
-db.createCS('testCS',{PageSize:4096.5})  
-db.createCS('testCS',{PageSize:})
 3、检查执行结果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -266,12 +220,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dropCS，删除系统CS</t>
-  </si>
-  <si>
-    <t>dropCS，指定CS名为空</t>
-  </si>
-  <si>
     <t>1、进入sdb，删除CS，CS名为空，覆盖如下取值：
 db.dropCS("")
 db.dropCS()
@@ -287,14 +235,6 @@
     <t>1、进入sdb，删除不存在的CS，如：
 db.dropCS("testCS"),其中testCS在sdb不存在
 2、检查执行结果</t>
-  </si>
-  <si>
-    <t>dropCS，删除不存在的CS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dropCS，删除为空和不为空的CS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1、进入sdb，删除为空和不为空的CS，如：
@@ -339,15 +279,9 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>getCS，获取不存在的CS</t>
-  </si>
-  <si>
     <t>语法：db.getCS(&lt; name &gt;)
 参数规格：
 name：string，必填，获取已存在的CS。不能获取系统CS。</t>
-  </si>
-  <si>
-    <t>getCS，指定的CS名为空</t>
   </si>
   <si>
     <t>1、进入sdb，获取指定的CS，CS名为空，覆盖如下取值：
@@ -365,9 +299,6 @@
 db.dropCS("testCS")，其中testCS在sdb不存在
 2、检查执行结果</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>listCollectionSpaces，加条件查询</t>
   </si>
   <si>
     <t>语法：db.listCollectionSpaces()
@@ -384,10 +315,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>createCS，覆盖name有效字符和边界</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>options:PageSize：默认为65536B，只能选填0，4096，8192，16384，32768，65536之一，0即默认为65536。非必填
 为兼容较早版本接口，db.createCS(&lt; name &gt;,[ PageSize ]) 同样可以工作。</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -399,30 +326,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>createCS，覆盖options：PageSize有效字符和边界</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>options:Domain，所属CS必须已经存在，且不能为 SYSDOMAIN。非必填</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>options:LobPageSize，只能选填0，4096，8192，16384，32768，65536，131072，262144，524288之一，0即为默认值262144。非必填</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCS，覆盖options:Domain有效字符和边界</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createCS，覆盖options:LobPageSize有效字符和边界</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>语法：db.createCS(&lt; name &gt;,[ options ])
-参数规格：
-name：string，必填，全局唯一，不能是空串，含点（.）或者美元符号（$）。且长度不超过127B。
-option非必填</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -486,6 +394,86 @@
     <t>1、CS删除失败，提示参数错误，提示信息合理准确
 2、日志打印信息合理准确</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：db.createCS(&lt; name &gt;,[ options ])
+参数规格：
+name：string，必填，全局唯一，不能是空串，含点（.）或者美元符号（$）。且长度不超过127B。
+option非必填</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CS，输入PageSize无效取值，覆盖如下取值：
+  a.无效取值：4096.5、-4096、4096.
+  b.空串
+如：
+db.createCS('testCS',{PageSize:4096.5})  
+db.createCS('testCS',{PageSize:})
+3、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCS，覆盖name有效字符和边界_st.verify.CS.001</t>
+  </si>
+  <si>
+    <t>createCS，覆盖options：PageSize有效字符和边界_st.verify.CS.002</t>
+  </si>
+  <si>
+    <t>createCS，覆盖options:Domain有效字符和边界_st.verify.CS.003</t>
+  </si>
+  <si>
+    <t>createCS，覆盖options:LobPageSize有效字符和边界_st.verify.CS.004</t>
+  </si>
+  <si>
+    <t>createCS，name重复_st.verify.CS.005</t>
+  </si>
+  <si>
+    <t>createCS，name字符无效_st.verify.CS.006</t>
+  </si>
+  <si>
+    <t>createCS，name长度无效_st.verify.CS.007</t>
+  </si>
+  <si>
+    <t>createCS，name参数不存在_st.verify.CS.008</t>
+  </si>
+  <si>
+    <t>createCS，options:PageSize无效取值_st.verify.CS.009</t>
+  </si>
+  <si>
+    <t>createCS，options:Domain指定的域不存在_st.verify.CS.010</t>
+  </si>
+  <si>
+    <t>createCS，options:Domain指定的域为系统域_st.verify.CS.011</t>
+  </si>
+  <si>
+    <t>createCS，options:Domain取值为空串_st.verify.CS.012</t>
+  </si>
+  <si>
+    <t>createCS，options:LobPageSize无效取值_st.verify.CS.013</t>
+  </si>
+  <si>
+    <t>createCS，格式错误_st.verify.CS.014</t>
+  </si>
+  <si>
+    <t>dropCS，删除为空和不为空的CS_st.verify.CS.015</t>
+  </si>
+  <si>
+    <t>dropCS，删除不存在的CS_st.verify.CS.016</t>
+  </si>
+  <si>
+    <t>dropCS，删除系统CS_st.verify.CS.017</t>
+  </si>
+  <si>
+    <t>dropCS，指定CS名为空_st.verify.CS.018</t>
+  </si>
+  <si>
+    <t>getCS，获取不存在的CS_st.verify.CS.019</t>
+  </si>
+  <si>
+    <t>getCS，指定的CS名为空_st.verify.CS.020</t>
+  </si>
+  <si>
+    <t>listCollectionSpaces，加条件查询_st.verify.CS.021</t>
   </si>
 </sst>
 </file>
@@ -984,7 +972,7 @@
     <col min="4" max="6" width="5" style="1" customWidth="1"/>
     <col min="7" max="7" width="41" style="1" customWidth="1"/>
     <col min="8" max="8" width="34" style="1" customWidth="1"/>
-    <col min="9" max="9" width="40.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="6.875" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1048,28 +1036,28 @@
     </row>
     <row r="3" spans="1:9" ht="121.5">
       <c r="A3" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="D3" s="4">
         <v>1</v>
       </c>
       <c r="E3" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="4">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I3" s="4">
         <v>1</v>
@@ -1077,400 +1065,541 @@
     </row>
     <row r="4" spans="1:9" ht="94.5">
       <c r="A4" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+        <v>49</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4">
+        <v>1</v>
+      </c>
       <c r="G4" s="2" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I4" s="4"/>
+        <v>54</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:9" ht="81">
       <c r="A5" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+        <v>49</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4">
+        <v>1</v>
+      </c>
       <c r="G5" s="2" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I5" s="4"/>
+        <v>56</v>
+      </c>
+      <c r="I5" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:9" ht="108">
       <c r="A6" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+        <v>49</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1</v>
+      </c>
       <c r="G6" s="2" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I6" s="4"/>
+        <v>58</v>
+      </c>
+      <c r="I6" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:9" ht="67.5">
       <c r="A7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="4">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="I7" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:9" ht="108">
       <c r="A8" s="2" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+      <c r="E8" s="4">
+        <v>2</v>
+      </c>
+      <c r="F8" s="4">
+        <v>1</v>
+      </c>
       <c r="G8" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I8" s="4"/>
+        <v>20</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:9" ht="108">
       <c r="A9" s="2" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+      <c r="E9" s="4">
+        <v>2</v>
+      </c>
+      <c r="F9" s="4">
+        <v>1</v>
+      </c>
       <c r="G9" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="4"/>
+        <v>21</v>
+      </c>
+      <c r="I9" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:9" ht="67.5">
       <c r="A10" s="2" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+      <c r="E10" s="4">
+        <v>2</v>
+      </c>
+      <c r="F10" s="4">
+        <v>1</v>
+      </c>
       <c r="G10" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I10" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="I10" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:9" ht="108">
       <c r="A11" s="2" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D11" s="4">
         <v>1</v>
       </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
+      <c r="E11" s="4">
+        <v>2</v>
+      </c>
+      <c r="F11" s="4">
+        <v>1</v>
+      </c>
       <c r="G11" s="2" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I11" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="I11" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:9" ht="67.5">
       <c r="A12" s="2" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
+      <c r="E12" s="4">
+        <v>2</v>
+      </c>
+      <c r="F12" s="4">
+        <v>1</v>
+      </c>
       <c r="G12" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I12" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="I12" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:9" ht="67.5">
       <c r="A13" s="2" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
       </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
+      <c r="E13" s="4">
+        <v>2</v>
+      </c>
+      <c r="F13" s="4">
+        <v>1</v>
+      </c>
       <c r="G13" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I13" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="I13" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="67.5">
       <c r="A14" s="2" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
       </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
+      <c r="E14" s="4">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4">
+        <v>1</v>
+      </c>
       <c r="G14" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I14" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="I14" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:9" ht="135">
       <c r="A15" s="2" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D15" s="4">
         <v>1</v>
       </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
+      <c r="E15" s="4">
+        <v>2</v>
+      </c>
+      <c r="F15" s="4">
+        <v>1</v>
+      </c>
       <c r="G15" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I15" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="I15" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:9" ht="189">
       <c r="A16" s="2" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D16" s="4">
         <v>1</v>
       </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
+      <c r="E16" s="4">
+        <v>2</v>
+      </c>
+      <c r="F16" s="4">
+        <v>1</v>
+      </c>
       <c r="G16" s="2" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I16" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="I16" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:9" ht="81">
       <c r="A17" s="2" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
       </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
+      <c r="E17" s="4">
+        <v>1</v>
+      </c>
+      <c r="F17" s="4">
+        <v>1</v>
+      </c>
       <c r="G17" s="2" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I17" s="4"/>
+        <v>40</v>
+      </c>
+      <c r="I17" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:9" ht="67.5">
       <c r="A18" s="2" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D18" s="4">
         <v>1</v>
       </c>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
+      <c r="E18" s="4">
+        <v>2</v>
+      </c>
+      <c r="F18" s="4">
+        <v>1</v>
+      </c>
       <c r="G18" s="2" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="I18" s="4"/>
+        <v>59</v>
+      </c>
+      <c r="I18" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:9" ht="67.5">
       <c r="A19" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D19" s="4">
         <v>1</v>
       </c>
+      <c r="E19" s="4">
+        <v>2</v>
+      </c>
+      <c r="F19" s="4">
+        <v>1</v>
+      </c>
       <c r="G19" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>83</v>
+        <v>60</v>
+      </c>
+      <c r="I19" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="67.5">
       <c r="A20" s="2" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D20" s="4">
         <v>1</v>
       </c>
+      <c r="E20" s="4">
+        <v>2</v>
+      </c>
+      <c r="F20" s="4">
+        <v>1</v>
+      </c>
       <c r="G20" s="2" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>84</v>
+        <v>61</v>
+      </c>
+      <c r="I20" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="67.5">
       <c r="A21" s="2" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D21" s="4">
         <v>1</v>
       </c>
+      <c r="E21" s="4">
+        <v>2</v>
+      </c>
+      <c r="F21" s="4">
+        <v>1</v>
+      </c>
       <c r="G21" s="2" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>61</v>
+        <v>44</v>
+      </c>
+      <c r="I21" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="67.5">
       <c r="A22" s="2" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D22" s="4">
         <v>1</v>
       </c>
+      <c r="E22" s="4">
+        <v>2</v>
+      </c>
+      <c r="F22" s="4">
+        <v>1</v>
+      </c>
       <c r="G22" s="2" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
+      </c>
+      <c r="I22" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="121.5">
       <c r="A23" s="2" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D23" s="4">
         <v>1</v>
       </c>
+      <c r="E23" s="4">
+        <v>1</v>
+      </c>
+      <c r="F23" s="4">
+        <v>1</v>
+      </c>
       <c r="G23" s="2" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
+      </c>
+      <c r="I23" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:9">
